--- a/data/processed/positivacao/2025-05_positivacao_anonimizado.xlsx
+++ b/data/processed/positivacao/2025-05_positivacao_anonimizado.xlsx
@@ -551,7 +551,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Vendedor: 1 - ROBSON</t>
+          <t>Vendedor: 1 - VENDEDOR 01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -26453,7 +26453,7 @@
     <row r="1005">
       <c r="A1005" t="inlineStr">
         <is>
-          <t>Vendedor: 3 - FERNANDA</t>
+          <t>Vendedor: 3 - VENDEDOR 03</t>
         </is>
       </c>
       <c r="B1005" t="inlineStr"/>
@@ -37649,7 +37649,7 @@
     <row r="1436">
       <c r="A1436" t="inlineStr">
         <is>
-          <t>Vendedor: 4 - DANIELA</t>
+          <t>Vendedor: 4 - VENDEDOR 04</t>
         </is>
       </c>
       <c r="B1436" t="inlineStr"/>
@@ -65995,7 +65995,7 @@
     <row r="2527">
       <c r="A2527" t="inlineStr">
         <is>
-          <t>Vendedor: 8 - RAFAEL</t>
+          <t>Vendedor: 8 - VENDEDOR 08</t>
         </is>
       </c>
       <c r="B2527" t="inlineStr"/>
@@ -67666,12 +67666,12 @@
       <c r="A2592" t="inlineStr"/>
       <c r="B2592" t="inlineStr">
         <is>
-          <t>Vendedor 1 - ROBSON: positivou 10 cliente(s), não positivou 85 cliente(s) - Total vendido: R$ 10.344,70
+          <t>Vendedor 1 - VENDEDOR 01: positivou 10 cliente(s), não positivou 85 cliente(s) - Total vendido: R$ 10.344,70
 Vendedor 18 - LOJA: positivou 245 cliente(s), não positivou 655 cliente(s) - Total vendido: R$ 69.701,71
-Vendedor 3 - FERNANDA: positivou 105 cliente(s), não positivou 325 cliente(s) - Total vendido: R$ 135.916,49
-Vendedor 4 - DANIELA: positivou 118 cliente(s), não positivou 526 cliente(s) - Total vendido: R$ 64.257,62
+Vendedor 3 - VENDEDOR 03: positivou 105 cliente(s), não positivou 325 cliente(s) - Total vendido: R$ 135.916,49
+Vendedor 4 - VENDEDOR 04: positivou 118 cliente(s), não positivou 526 cliente(s) - Total vendido: R$ 64.257,62
 Vendedor 5 - SITE: positivou 0 cliente(s), não positivou 445 cliente(s) - Total vendido: R$ 0,00
-Vendedor 8 - RAFAEL: positivou 2 cliente(s), não positivou 61 cliente(s) - Total vendido: R$ 557,80</t>
+Vendedor 8 - VENDEDOR 08: positivou 2 cliente(s), não positivou 61 cliente(s) - Total vendido: R$ 557,80</t>
         </is>
       </c>
       <c r="C2592" t="inlineStr"/>
